--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
@@ -138,15 +138,15 @@
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
     <t xml:space="preserve">Viña del Mar</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:47</t>
+    <t xml:space="preserve">2026-09-10 00:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1181,7 +1181,7 @@
         <v>40</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5703</v>
+        <v>5502</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -1194,7 +1194,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5109</v>
+        <v>5703</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1207,7 +1207,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5502</v>
+        <v>5109</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:56</t>
+    <t xml:space="preserve">2026-09-18 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
@@ -138,15 +138,15 @@
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:04</t>
+    <t xml:space="preserve">2026-09-23 14:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1181,9 +1181,11 @@
         <v>40</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5502</v>
-      </c>
-      <c r="D37" s="2"/>
+        <v>5109</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
@@ -1194,9 +1196,11 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5703</v>
-      </c>
-      <c r="D38" s="2"/>
+        <v>5502</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
@@ -1207,9 +1211,11 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5109</v>
-      </c>
-      <c r="D39" s="2"/>
+        <v>5703</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E39" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:26</t>
+    <t xml:space="preserve">2026-10-02 15:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:33</t>
+    <t xml:space="preserve">2026-10-04 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:13</t>
+    <t xml:space="preserve">2026-10-05 14:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -847,7 +847,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="18">
